--- a/ITEST/itest.WebService/openl-repository/EPBDS-7947/datatype-validation/datatype-validation.xlsx
+++ b/ITEST/itest.WebService/openl-repository/EPBDS-7947/datatype-validation/datatype-validation.xlsx
@@ -144,7 +144,7 @@
     <t>Datatype BrandCode &lt;Integer&gt;</t>
   </si>
   <si>
-    <t>for (int i = 0; i &lt; policies.length; i++)</t>
+    <t>for (int i = 0; i &lt; policies.length; i += 1)</t>
   </si>
   <si>
     <t xml:space="preserve">    checkValidation(policies[i]);</t>
